--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15360" windowHeight="10480"/>
+    <workbookView windowWidth="25600" windowHeight="10480" activeTab="5"/>
   </bookViews>
   <sheets>
-    <sheet name="需求列表" sheetId="5" r:id="rId1"/>
-    <sheet name="用户故事" sheetId="1" r:id="rId2"/>
-    <sheet name="Sprint1迭代计划" sheetId="2" r:id="rId3"/>
-    <sheet name="SprintN迭代计划 " sheetId="6" r:id="rId4"/>
-    <sheet name="迭代回顾" sheetId="4" r:id="rId5"/>
+    <sheet name="需求列表" sheetId="1" r:id="rId1"/>
+    <sheet name="用户故事" sheetId="2" r:id="rId2"/>
+    <sheet name="Sprint1迭代计划 " sheetId="6" r:id="rId3"/>
+    <sheet name="Sprint2迭代计划" sheetId="3" r:id="rId4"/>
+    <sheet name="SprintN迭代计划 " sheetId="4" r:id="rId5"/>
+    <sheet name="迭代回顾" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="126">
   <si>
     <t>模块</t>
   </si>
@@ -105,6 +106,48 @@
     <t>收藏列表</t>
   </si>
   <si>
+    <t>活动相册模块</t>
+  </si>
+  <si>
+    <t>相册上传</t>
+  </si>
+  <si>
+    <t>相册展示</t>
+  </si>
+  <si>
+    <t>活动标签与话题模块</t>
+  </si>
+  <si>
+    <t>活动标签</t>
+  </si>
+  <si>
+    <t>标签筛选</t>
+  </si>
+  <si>
+    <t>活动话题</t>
+  </si>
+  <si>
+    <t>搜索与筛选模块</t>
+  </si>
+  <si>
+    <t>关键词搜索</t>
+  </si>
+  <si>
+    <t>多维度筛选</t>
+  </si>
+  <si>
+    <t>智能搜索</t>
+  </si>
+  <si>
+    <t>活动订阅模块</t>
+  </si>
+  <si>
+    <t>活动订阅</t>
+  </si>
+  <si>
+    <t>通知推送</t>
+  </si>
+  <si>
     <t>系统管理员模块</t>
   </si>
   <si>
@@ -120,27 +163,6 @@
     <t>数据统计</t>
   </si>
   <si>
-    <t>活动管理</t>
-  </si>
-  <si>
-    <t>发布活动、编辑活动、删除活动。</t>
-  </si>
-  <si>
-    <t>用户报名活动、查看报名信息。</t>
-  </si>
-  <si>
-    <t>评论互动</t>
-  </si>
-  <si>
-    <t>用户评论活动。</t>
-  </si>
-  <si>
-    <t>收藏</t>
-  </si>
-  <si>
-    <t>收藏感兴趣的活动。</t>
-  </si>
-  <si>
     <t>用户故事</t>
   </si>
   <si>
@@ -159,13 +181,22 @@
     <t>备注</t>
   </si>
   <si>
-    <t>作为一个用户，我需要注册新用户从而使用这个系统</t>
+    <t>作为一个新用户，我想要通过学号/工号和邮箱注册账号，以便于使用平台的所有功能。</t>
   </si>
   <si>
     <t>P0</t>
   </si>
   <si>
-    <t>Sprint1 (2016/03/24~2026/04/7)</t>
+    <t>作为一个已注册用户，我想要通过账号和密码登录系统，以便于访问我的个人主页和使用平台功能。</t>
+  </si>
+  <si>
+    <t>作为一个忘记密码的用户，我想要通过邮箱找回密码，以便于重新登录系统。</t>
+  </si>
+  <si>
+    <t>作为一个登录用户，我想要修改我的登录密码，以便于提高账号安全性。</t>
+  </si>
+  <si>
+    <t>Sprint1 (2026/04/09~2026/04/23)</t>
   </si>
   <si>
     <t>任务</t>
@@ -177,46 +208,205 @@
     <t>负责人</t>
   </si>
   <si>
+    <t>状态</t>
+  </si>
+  <si>
     <t>Sprint1</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>数据库设计与初始化</t>
+  </si>
+  <si>
+    <t>开发A</t>
+  </si>
+  <si>
+    <t>DONE</t>
+  </si>
+  <si>
+    <t>1.1.1 用户注册</t>
+  </si>
+  <si>
+    <t>用户注册功能开发</t>
+  </si>
+  <si>
+    <t>TODO</t>
+  </si>
+  <si>
+    <t>用户注册功能测试</t>
+  </si>
+  <si>
+    <t>1.1.2 用户登录</t>
+  </si>
+  <si>
+    <t>用户登录功能开发</t>
+  </si>
+  <si>
+    <t>用户登录功能测试</t>
+  </si>
+  <si>
+    <t>1.1.3 忘记密码</t>
+  </si>
+  <si>
+    <t>忘记密码功能开发</t>
+  </si>
+  <si>
+    <t>1.2.1 查看个人信息</t>
+  </si>
+  <si>
+    <t>查看个人信息开发</t>
+  </si>
+  <si>
+    <t>1.2.2 修改个人资料</t>
+  </si>
+  <si>
+    <t>修改个人资料开发</t>
+  </si>
+  <si>
+    <t>1.2.3 修改密码</t>
+  </si>
+  <si>
+    <t>修改密码开发</t>
+  </si>
+  <si>
+    <t>忘记密码功能测试</t>
+  </si>
+  <si>
+    <t>Sprint1 (2016/0x/xx~2026/0x/xx)</t>
+  </si>
+  <si>
+    <t>2.1 发布活动</t>
+  </si>
+  <si>
+    <t>发布活动功能开发</t>
+  </si>
+  <si>
+    <t>开发B</t>
+  </si>
+  <si>
+    <t>发布活动功能测试</t>
+  </si>
+  <si>
+    <t>2.2 编辑活动</t>
+  </si>
+  <si>
+    <t>编辑活动功能开发</t>
+  </si>
+  <si>
+    <t>2.3 删除活动</t>
+  </si>
+  <si>
+    <t>删除活动功能开发</t>
+  </si>
+  <si>
+    <t>2.4 活动列表管理</t>
+  </si>
+  <si>
+    <t>活动列表管理开发</t>
+  </si>
+  <si>
+    <t>3.1 活动报名</t>
+  </si>
+  <si>
+    <t>活动报名功能开发</t>
+  </si>
+  <si>
+    <t>活动报名功能测试</t>
+  </si>
+  <si>
+    <t>3.2 报名信息查看</t>
+  </si>
+  <si>
+    <t>报名信息查看开发</t>
+  </si>
+  <si>
+    <t>3.3 报名状态管理</t>
+  </si>
+  <si>
+    <t>报名状态管理开发</t>
+  </si>
+  <si>
+    <t>4.1 活动评论</t>
+  </si>
+  <si>
+    <t>活动评论开发</t>
+  </si>
+  <si>
+    <t>开发C</t>
+  </si>
+  <si>
+    <t>4.2 评论查看</t>
+  </si>
+  <si>
+    <t>评论查看开发</t>
+  </si>
+  <si>
+    <t>5.1 活动收藏</t>
+  </si>
+  <si>
+    <t>活动收藏开发</t>
+  </si>
+  <si>
+    <t>5.2 收藏列表</t>
+  </si>
+  <si>
+    <t>收藏列表开发</t>
+  </si>
+  <si>
+    <t>8.1 关键词搜索</t>
+  </si>
+  <si>
+    <t>关键词搜索开发</t>
+  </si>
+  <si>
+    <t>8.2 多维度筛选</t>
+  </si>
+  <si>
+    <t>多维度筛选开发</t>
+  </si>
+  <si>
+    <t>前端页面搭建</t>
+  </si>
+  <si>
+    <t>前后端联调</t>
+  </si>
+  <si>
+    <t>集成测试</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>做得好的</t>
+  </si>
+  <si>
+    <t>需要改进</t>
+  </si>
+  <si>
+    <t>行动项</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>用户登录功能</t>
+  </si>
+  <si>
+    <t>陈明航</t>
+  </si>
+  <si>
     <t>用户注册</t>
   </si>
   <si>
-    <t>用户注册开发</t>
-  </si>
-  <si>
-    <t>张三</t>
-  </si>
-  <si>
-    <t>用户注册测试</t>
-  </si>
-  <si>
-    <t>李四</t>
-  </si>
-  <si>
-    <t>Sprint1 (2016/0x/xx~2026/0x/xx)</t>
-  </si>
-  <si>
-    <t>用户退出登录</t>
-  </si>
-  <si>
-    <t>退出登录开发</t>
-  </si>
-  <si>
-    <t>退出登录测试</t>
-  </si>
-  <si>
-    <t>做得好的</t>
-  </si>
-  <si>
-    <t>需要改进</t>
-  </si>
-  <si>
-    <t>行动项</t>
-  </si>
-  <si>
-    <t>Sprint 1</t>
+    <t>项目结构调整</t>
+  </si>
+  <si>
+    <t>刘晓飞</t>
   </si>
   <si>
     <t>Sprint 2</t>
@@ -232,7 +422,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -265,13 +455,6 @@
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -418,7 +601,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -476,12 +659,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -733,152 +910,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -889,23 +1066,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -969,7 +1140,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表2" displayName="表2" ref="A1:F22" totalsRowShown="0">
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F22" etc:filterBottomFollowUsedRange="0"/>
   <tableColumns count="6">
     <tableColumn id="2" name="用户故事"/>
@@ -1268,7 +1439,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.4545454545455" customWidth="1"/>
@@ -1277,18 +1448,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -1296,71 +1467,50 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
       <c r="B3" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
       <c r="B4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -1368,26 +1518,20 @@
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="7"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B17" t="s">
@@ -1395,18 +1539,15 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="8" t="s">
-        <v>18</v>
-      </c>
       <c r="B18" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="8"/>
+      <c r="A19" s="7"/>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B20" t="s">
@@ -1414,18 +1555,15 @@
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="B21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="8"/>
+      <c r="A22" s="7"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" t="s">
@@ -1433,62 +1571,101 @@
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="8" t="s">
-        <v>24</v>
-      </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" s="2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="8" t="s">
-        <v>24</v>
       </c>
       <c r="B26" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="2:3">
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="B34" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3">
+        <v>36</v>
+      </c>
+      <c r="C34" s="6"/>
+    </row>
+    <row r="35" spans="1:3">
       <c r="B35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3">
-      <c r="B36" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3">
+        <v>37</v>
+      </c>
+      <c r="C35" s="6"/>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="C36" s="6"/>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
+      </c>
+      <c r="C37" s="6"/>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="B40" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A23:A24"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A37:A40"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
@@ -1497,10 +1674,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="5"/>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="59.5272727272727" customWidth="1"/>
+    <col min="1" max="1" width="99.4545454545455" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="23.8636363636364" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
@@ -1509,34 +1686,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>41</v>
+      <c r="A1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="6" t="s">
-        <v>42</v>
+      <c r="A2" t="s">
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C2">
         <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1551,8 +1743,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="26.7272727272727" customWidth="1"/>
@@ -1563,69 +1755,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="B1" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>62</v>
+      </c>
+      <c r="F3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D4">
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>53</v>
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1635,67 +1909,159 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="24.1363636363636" customWidth="1"/>
-    <col min="5" max="7" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="3" width="26.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="26.8" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>58</v>
+      </c>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="D4" t="s">
-        <v>53</v>
+      <c r="E3"/>
+      <c r="F3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4"/>
+      <c r="C4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D4"/>
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5"/>
+      <c r="C5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="C9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1710,53 +2076,500 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="24.1363636363636" customWidth="1"/>
+    <col min="5" max="7" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+      <c r="D17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>100</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>105</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>107</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29">
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>100</v>
+      </c>
+      <c r="E29" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" t="s">
+        <v>100</v>
+      </c>
+      <c r="E30" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
+        <v>115</v>
+      </c>
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" t="s">
+        <v>79</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>62</v>
+      </c>
+      <c r="F36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>59</v>
+      </c>
+      <c r="B37" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F37" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="5" width="22" customWidth="1"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="33.9090909090909" customWidth="1"/>
+    <col min="3" max="5" width="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>116</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>117</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2"/>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
+      <c r="C4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
+        <v>125</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/敏捷开发Sprint追踪表.xlsx
+++ b/敏捷开发Sprint追踪表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10480" activeTab="5"/>
+    <workbookView windowWidth="25600" windowHeight="10480" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="1" r:id="rId1"/>
@@ -1877,7 +1877,7 @@
         <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1959,20 +1959,17 @@
       <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3"/>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="B4"/>
       <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4"/>
       <c r="F4" t="s">
         <v>66</v>
       </c>
@@ -1981,14 +1978,12 @@
       <c r="A5" t="s">
         <v>59</v>
       </c>
-      <c r="B5"/>
       <c r="C5" t="s">
         <v>70</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5"/>
       <c r="F5" t="s">
         <v>66</v>
       </c>
@@ -2536,7 +2531,6 @@
       <c r="B2" t="s">
         <v>120</v>
       </c>
-      <c r="C2"/>
       <c r="D2" t="s">
         <v>7</v>
       </c>
